--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -27899,21 +27887,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Brazil WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Coverage: 2022-01-01 to 2026-03-22 | Publication days: 631</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -27921,22 +27909,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1543"/>
+  <dimension ref="A1:E1544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27625,13 +27625,13 @@
         </is>
       </c>
       <c r="B1530" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C1530" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -27647,10 +27647,10 @@
         <v>0</v>
       </c>
       <c r="C1531" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -27664,10 +27664,10 @@
       </c>
       <c r="B1532" t="inlineStr"/>
       <c r="C1532" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -27683,10 +27683,10 @@
         <v>0</v>
       </c>
       <c r="C1533" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -27702,10 +27702,10 @@
         <v>-2</v>
       </c>
       <c r="C1534" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -27719,10 +27719,10 @@
       </c>
       <c r="B1535" t="inlineStr"/>
       <c r="C1535" t="n">
-        <v>-1</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="E1535" t="b">
         <v>0</v>
@@ -27736,10 +27736,10 @@
       </c>
       <c r="B1536" t="inlineStr"/>
       <c r="C1536" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1536" t="b">
         <v>0</v>
@@ -27756,7 +27756,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1537" t="b">
         <v>0</v>
@@ -27773,7 +27773,7 @@
         <v>-1.428571428571429</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="E1538" t="b">
         <v>0</v>
@@ -27792,7 +27792,7 @@
         <v>-1.428571428571429</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -27809,7 +27809,7 @@
         <v>-1.428571428571429</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -27826,7 +27826,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="E1541" t="b">
         <v>0</v>
@@ -27843,7 +27843,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="E1542" t="b">
         <v>0</v>
@@ -27860,9 +27860,26 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="E1543" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr"/>
+      <c r="C1544" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D1544" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E1544" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27896,7 +27913,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-03-22 | Publication days: 631</t>
+          <t>Coverage: 2022-01-01 to 2026-03-23 | Publication days: 631</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1544"/>
+  <dimension ref="A1:E1545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27880,6 +27880,23 @@
         <v>-0.7</v>
       </c>
       <c r="E1544" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr"/>
+      <c r="C1545" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1545" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E1545" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27913,7 +27930,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-03-23 | Publication days: 631</t>
+          <t>Coverage: 2022-01-01 to 2026-03-24 | Publication days: 631</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1545"/>
+  <dimension ref="A1:E1546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27897,6 +27897,23 @@
         <v>-0.7</v>
       </c>
       <c r="E1545" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr"/>
+      <c r="C1546" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1546" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E1546" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27930,7 +27947,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-03-24 | Publication days: 631</t>
+          <t>Coverage: 2022-01-01 to 2026-03-25 | Publication days: 631</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -27821,7 +27821,9 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="B1541" t="inlineStr"/>
+      <c r="B1541" t="n">
+        <v>0</v>
+      </c>
       <c r="C1541" t="n">
         <v>-1.142857142857143</v>
       </c>
@@ -27829,7 +27831,7 @@
         <v>-0.7</v>
       </c>
       <c r="E1541" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1542">
@@ -27872,7 +27874,9 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="B1544" t="inlineStr"/>
+      <c r="B1544" t="n">
+        <v>0</v>
+      </c>
       <c r="C1544" t="n">
         <v>-0.2857142857142857</v>
       </c>
@@ -27880,7 +27884,7 @@
         <v>-0.7</v>
       </c>
       <c r="E1544" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1545">
@@ -27889,7 +27893,9 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="B1545" t="inlineStr"/>
+      <c r="B1545" t="n">
+        <v>0</v>
+      </c>
       <c r="C1545" t="n">
         <v>0</v>
       </c>
@@ -27897,7 +27903,7 @@
         <v>-0.7</v>
       </c>
       <c r="E1545" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1546">
@@ -27947,7 +27953,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-03-25 | Publication days: 631</t>
+          <t>Coverage: 2022-01-01 to 2026-03-25 | Publication days: 634</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -27944,21 +27956,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Brazil WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2022-01-01 to 2026-03-25 | Publication days: 634</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -27966,22 +27978,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1546"/>
+  <dimension ref="A1:E1547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -27932,6 +27920,23 @@
         <v>-0.7</v>
       </c>
       <c r="E1546" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr"/>
+      <c r="C1547" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1547" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E1547" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27956,21 +27961,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Brazil WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2022-01-01 to 2026-03-25 | Publication days: 634</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2022-01-01 to 2026-03-26 | Publication days: 634</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -27978,22 +27983,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -27961,21 +27973,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Brazil WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2022-01-01 to 2026-03-26 | Publication days: 634</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -27983,22 +27995,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -27973,21 +27961,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Brazil WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Coverage: 2022-01-01 to 2026-03-26 | Publication days: 634</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -27995,22 +27983,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1547"/>
+  <dimension ref="A1:E1548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -27924,7 +27912,9 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="B1546" t="inlineStr"/>
+      <c r="B1546" t="n">
+        <v>0</v>
+      </c>
       <c r="C1546" t="n">
         <v>0</v>
       </c>
@@ -27932,7 +27922,7 @@
         <v>-0.7</v>
       </c>
       <c r="E1546" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1547">
@@ -27941,7 +27931,9 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="B1547" t="inlineStr"/>
+      <c r="B1547" t="n">
+        <v>0</v>
+      </c>
       <c r="C1547" t="n">
         <v>0</v>
       </c>
@@ -27949,6 +27941,23 @@
         <v>-0.7</v>
       </c>
       <c r="E1547" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr"/>
+      <c r="C1548" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1548" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E1548" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27973,21 +27982,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Brazil WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2022-01-01 to 2026-03-26 | Publication days: 634</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2022-01-01 to 2026-03-27 | Publication days: 636</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -27995,22 +28004,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -27950,7 +27950,9 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B1548" t="inlineStr"/>
+      <c r="B1548" t="n">
+        <v>0</v>
+      </c>
       <c r="C1548" t="n">
         <v>0</v>
       </c>
@@ -27958,7 +27960,7 @@
         <v>-0.7</v>
       </c>
       <c r="E1548" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -27991,7 +27993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-03-27 | Publication days: 636</t>
+          <t>Coverage: 2022-01-01 to 2026-03-27 | Publication days: 637</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1548"/>
+  <dimension ref="A1:E1549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27961,6 +27961,23 @@
       </c>
       <c r="E1548" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr"/>
+      <c r="C1549" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1549" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E1549" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27993,7 +28010,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-03-27 | Publication days: 637</t>
+          <t>Coverage: 2022-01-01 to 2026-03-28 | Publication days: 637</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1549"/>
+  <dimension ref="A1:E1550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27977,6 +27977,23 @@
         <v>-0.7</v>
       </c>
       <c r="E1549" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr"/>
+      <c r="C1550" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1550" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E1550" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28010,7 +28027,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-03-28 | Publication days: 637</t>
+          <t>Coverage: 2022-01-01 to 2026-03-29 | Publication days: 637</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1550"/>
+  <dimension ref="A1:E1551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27994,6 +27994,23 @@
         <v>-0.6333333333333333</v>
       </c>
       <c r="E1550" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr"/>
+      <c r="C1551" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1551" t="n">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="E1551" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28027,7 +28044,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-03-29 | Publication days: 637</t>
+          <t>Coverage: 2022-01-01 to 2026-03-30 | Publication days: 637</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1551"/>
+  <dimension ref="A1:E1552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27969,7 +27969,9 @@
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="B1549" t="inlineStr"/>
+      <c r="B1549" t="n">
+        <v>0</v>
+      </c>
       <c r="C1549" t="n">
         <v>0</v>
       </c>
@@ -27977,7 +27979,7 @@
         <v>-0.7</v>
       </c>
       <c r="E1549" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1550">
@@ -28012,6 +28014,25 @@
       </c>
       <c r="E1551" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1552" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1552" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1552" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E1552" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -28044,7 +28065,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-03-30 | Publication days: 637</t>
+          <t>Coverage: 2022-01-01 to 2026-03-31 | Publication days: 639</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1552"/>
+  <dimension ref="A1:E1553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28023,16 +28023,33 @@
         </is>
       </c>
       <c r="B1552" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1552" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1552" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1552" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr"/>
+      <c r="C1553" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D1553" t="n">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="E1553" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -28065,7 +28082,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-03-31 | Publication days: 639</t>
+          <t>Coverage: 2022-01-01 to 2026-04-01 | Publication days: 639</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1553"/>
+  <dimension ref="A1:E1554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28041,7 +28041,9 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="B1553" t="inlineStr"/>
+      <c r="B1553" t="n">
+        <v>-2</v>
+      </c>
       <c r="C1553" t="n">
         <v>-0.5714285714285714</v>
       </c>
@@ -28049,6 +28051,23 @@
         <v>-0.5333333333333333</v>
       </c>
       <c r="E1553" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr"/>
+      <c r="C1554" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D1554" t="n">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="E1554" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28082,7 +28101,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-04-01 | Publication days: 639</t>
+          <t>Coverage: 2022-01-01 to 2026-04-02 | Publication days: 640</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1554"/>
+  <dimension ref="A1:E1555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28068,6 +28068,23 @@
         <v>-0.5333333333333333</v>
       </c>
       <c r="E1554" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr"/>
+      <c r="C1555" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="D1555" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E1555" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28101,7 +28118,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-04-02 | Publication days: 640</t>
+          <t>Coverage: 2022-01-01 to 2026-04-03 | Publication days: 640</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1555"/>
+  <dimension ref="A1:E1556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28085,6 +28085,23 @@
         <v>-0.6</v>
       </c>
       <c r="E1555" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr"/>
+      <c r="C1556" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D1556" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E1556" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28118,7 +28135,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-04-03 | Publication days: 640</t>
+          <t>Coverage: 2022-01-01 to 2026-04-04 | Publication days: 640</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1556"/>
+  <dimension ref="A1:E1557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28102,6 +28102,23 @@
         <v>-0.6666666666666666</v>
       </c>
       <c r="E1556" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr"/>
+      <c r="C1557" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="D1557" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E1557" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28135,7 +28152,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-04-04 | Publication days: 640</t>
+          <t>Coverage: 2022-01-01 to 2026-04-05 | Publication days: 640</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1557"/>
+  <dimension ref="A1:E1558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28119,6 +28119,23 @@
         <v>-0.7333333333333333</v>
       </c>
       <c r="E1557" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr"/>
+      <c r="C1558" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D1558" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E1558" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28152,7 +28169,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-04-05 | Publication days: 640</t>
+          <t>Coverage: 2022-01-01 to 2026-04-06 | Publication days: 640</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1558"/>
+  <dimension ref="A1:E1559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28136,6 +28136,23 @@
         <v>-0.8</v>
       </c>
       <c r="E1558" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr"/>
+      <c r="C1559" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D1559" t="n">
+        <v>-0.8666666666666667</v>
+      </c>
+      <c r="E1559" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28169,7 +28186,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-04-06 | Publication days: 640</t>
+          <t>Coverage: 2022-01-01 to 2026-04-07 | Publication days: 640</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1559"/>
+  <dimension ref="A1:E1560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27138,13 +27138,13 @@
         </is>
       </c>
       <c r="B1503" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1503" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1503" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1503" t="b">
         <v>1</v>
@@ -27160,10 +27160,10 @@
         <v>0</v>
       </c>
       <c r="C1504" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1504" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1504" t="b">
         <v>1</v>
@@ -27179,10 +27179,10 @@
         <v>0</v>
       </c>
       <c r="C1505" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1505" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1505" t="b">
         <v>1</v>
@@ -27198,10 +27198,10 @@
         <v>0</v>
       </c>
       <c r="C1506" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1506" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1506" t="b">
         <v>1</v>
@@ -27215,10 +27215,10 @@
       </c>
       <c r="B1507" t="inlineStr"/>
       <c r="C1507" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1507" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1507" t="b">
         <v>0</v>
@@ -27232,10 +27232,10 @@
       </c>
       <c r="B1508" t="inlineStr"/>
       <c r="C1508" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1508" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1508" t="b">
         <v>0</v>
@@ -27249,10 +27249,10 @@
       </c>
       <c r="B1509" t="inlineStr"/>
       <c r="C1509" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1509" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1509" t="b">
         <v>0</v>
@@ -27271,7 +27271,7 @@
         <v>0</v>
       </c>
       <c r="D1510" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1510" t="b">
         <v>1</v>
@@ -27288,7 +27288,7 @@
         <v>0</v>
       </c>
       <c r="D1511" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1511" t="b">
         <v>0</v>
@@ -27305,7 +27305,7 @@
         <v>0</v>
       </c>
       <c r="D1512" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1512" t="b">
         <v>0</v>
@@ -27324,7 +27324,7 @@
         <v>0</v>
       </c>
       <c r="D1513" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3</v>
       </c>
       <c r="E1513" t="b">
         <v>1</v>
@@ -27341,7 +27341,7 @@
         <v>0</v>
       </c>
       <c r="D1514" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1514" t="b">
         <v>0</v>
@@ -27358,7 +27358,7 @@
         <v>0</v>
       </c>
       <c r="D1515" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.1</v>
       </c>
       <c r="E1515" t="b">
         <v>0</v>
@@ -27377,7 +27377,7 @@
         <v>0</v>
       </c>
       <c r="D1516" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1516" t="b">
         <v>1</v>
@@ -27394,7 +27394,7 @@
         <v>0</v>
       </c>
       <c r="D1517" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1517" t="b">
         <v>0</v>
@@ -27411,7 +27411,7 @@
         <v>0</v>
       </c>
       <c r="D1518" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1518" t="b">
         <v>0</v>
@@ -27428,7 +27428,7 @@
         <v>0</v>
       </c>
       <c r="D1519" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1519" t="b">
         <v>0</v>
@@ -27447,7 +27447,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1520" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1520" t="b">
         <v>1</v>
@@ -27466,7 +27466,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1521" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1521" t="b">
         <v>1</v>
@@ -27485,7 +27485,7 @@
         <v>-1</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.3</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -27502,7 +27502,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3</v>
       </c>
       <c r="E1523" t="b">
         <v>0</v>
@@ -27521,7 +27521,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -27540,7 +27540,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -27559,7 +27559,7 @@
         <v>-1.571428571428571</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -27578,7 +27578,7 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -27595,7 +27595,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1528" t="b">
         <v>0</v>
@@ -27612,7 +27612,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -27631,7 +27631,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -27650,7 +27650,7 @@
         <v>0</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -27667,7 +27667,7 @@
         <v>0</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -27699,13 +27699,13 @@
         </is>
       </c>
       <c r="B1534" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1534" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -27719,10 +27719,10 @@
       </c>
       <c r="B1535" t="inlineStr"/>
       <c r="C1535" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.5</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1535" t="b">
         <v>0</v>
@@ -27736,10 +27736,10 @@
       </c>
       <c r="B1536" t="inlineStr"/>
       <c r="C1536" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1536" t="b">
         <v>0</v>
@@ -27753,10 +27753,10 @@
       </c>
       <c r="B1537" t="inlineStr"/>
       <c r="C1537" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1537" t="b">
         <v>0</v>
@@ -27770,10 +27770,10 @@
       </c>
       <c r="B1538" t="inlineStr"/>
       <c r="C1538" t="n">
-        <v>-1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.7</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1538" t="b">
         <v>0</v>
@@ -27789,10 +27789,10 @@
         <v>0</v>
       </c>
       <c r="C1539" t="n">
-        <v>-1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.7</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -27806,10 +27806,10 @@
       </c>
       <c r="B1540" t="inlineStr"/>
       <c r="C1540" t="n">
-        <v>-1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.7</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -27825,10 +27825,10 @@
         <v>0</v>
       </c>
       <c r="C1541" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.7</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1541" t="b">
         <v>1</v>
@@ -27842,10 +27842,10 @@
       </c>
       <c r="B1542" t="inlineStr"/>
       <c r="C1542" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.7</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1542" t="b">
         <v>0</v>
@@ -27859,10 +27859,10 @@
       </c>
       <c r="B1543" t="inlineStr"/>
       <c r="C1543" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.7</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1543" t="b">
         <v>0</v>
@@ -27878,10 +27878,10 @@
         <v>0</v>
       </c>
       <c r="C1544" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1544" t="n">
-        <v>-0.7</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1544" t="b">
         <v>1</v>
@@ -27900,7 +27900,7 @@
         <v>0</v>
       </c>
       <c r="D1545" t="n">
-        <v>-0.7</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1545" t="b">
         <v>1</v>
@@ -27919,7 +27919,7 @@
         <v>0</v>
       </c>
       <c r="D1546" t="n">
-        <v>-0.7</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1546" t="b">
         <v>1</v>
@@ -27938,7 +27938,7 @@
         <v>0</v>
       </c>
       <c r="D1547" t="n">
-        <v>-0.7</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1547" t="b">
         <v>1</v>
@@ -27957,7 +27957,7 @@
         <v>0</v>
       </c>
       <c r="D1548" t="n">
-        <v>-0.7</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1548" t="b">
         <v>1</v>
@@ -27976,7 +27976,7 @@
         <v>0</v>
       </c>
       <c r="D1549" t="n">
-        <v>-0.7</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1549" t="b">
         <v>1</v>
@@ -27993,7 +27993,7 @@
         <v>0</v>
       </c>
       <c r="D1550" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1550" t="b">
         <v>0</v>
@@ -28010,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="D1551" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E1551" t="b">
         <v>0</v>
@@ -28029,7 +28029,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1552" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E1552" t="b">
         <v>1</v>
@@ -28048,7 +28048,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1553" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E1553" t="b">
         <v>1</v>
@@ -28065,7 +28065,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1554" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E1554" t="b">
         <v>0</v>
@@ -28082,7 +28082,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D1555" t="n">
-        <v>-0.6</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1555" t="b">
         <v>0</v>
@@ -28099,7 +28099,7 @@
         <v>-1.428571428571429</v>
       </c>
       <c r="D1556" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1556" t="b">
         <v>0</v>
@@ -28116,7 +28116,7 @@
         <v>-1.714285714285714</v>
       </c>
       <c r="D1557" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1557" t="b">
         <v>0</v>
@@ -28133,7 +28133,7 @@
         <v>-2</v>
       </c>
       <c r="D1558" t="n">
-        <v>-0.8</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1558" t="b">
         <v>0</v>
@@ -28150,10 +28150,29 @@
         <v>-2</v>
       </c>
       <c r="D1559" t="n">
-        <v>-0.8666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1559" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1560" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1560" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D1560" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E1560" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -28186,7 +28205,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-04-07 | Publication days: 640</t>
+          <t>Coverage: 2022-01-01 to 2026-04-08 | Publication days: 641</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1560"/>
+  <dimension ref="A1:E1561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27479,13 +27479,13 @@
         </is>
       </c>
       <c r="B1522" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1522" t="n">
-        <v>-1</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -27499,10 +27499,10 @@
       </c>
       <c r="B1523" t="inlineStr"/>
       <c r="C1523" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.3</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1523" t="b">
         <v>0</v>
@@ -27515,13 +27515,13 @@
         </is>
       </c>
       <c r="B1524" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1524" t="n">
-        <v>-1.571428571428571</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -27537,10 +27537,10 @@
         <v>0</v>
       </c>
       <c r="C1525" t="n">
-        <v>-1.571428571428571</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -27556,10 +27556,10 @@
         <v>0</v>
       </c>
       <c r="C1526" t="n">
-        <v>-1.571428571428571</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -27575,10 +27575,10 @@
         <v>0</v>
       </c>
       <c r="C1527" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -27592,10 +27592,10 @@
       </c>
       <c r="B1528" t="inlineStr"/>
       <c r="C1528" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1528" t="b">
         <v>0</v>
@@ -27609,10 +27609,10 @@
       </c>
       <c r="B1529" t="inlineStr"/>
       <c r="C1529" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -27628,10 +27628,10 @@
         <v>0</v>
       </c>
       <c r="C1530" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -27650,7 +27650,7 @@
         <v>0</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -27667,7 +27667,7 @@
         <v>0</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -27686,7 +27686,7 @@
         <v>0</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -27705,7 +27705,7 @@
         <v>0</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -27722,7 +27722,7 @@
         <v>0</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1535" t="b">
         <v>0</v>
@@ -27739,7 +27739,7 @@
         <v>0</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1536" t="b">
         <v>0</v>
@@ -27756,7 +27756,7 @@
         <v>0</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1537" t="b">
         <v>0</v>
@@ -27773,7 +27773,7 @@
         <v>0</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1538" t="b">
         <v>0</v>
@@ -27792,7 +27792,7 @@
         <v>0</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -27809,7 +27809,7 @@
         <v>0</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -27828,7 +27828,7 @@
         <v>0</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1541" t="b">
         <v>1</v>
@@ -27845,7 +27845,7 @@
         <v>0</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1542" t="b">
         <v>0</v>
@@ -27862,7 +27862,7 @@
         <v>0</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1543" t="b">
         <v>0</v>
@@ -27881,7 +27881,7 @@
         <v>0</v>
       </c>
       <c r="D1544" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1544" t="b">
         <v>1</v>
@@ -27900,7 +27900,7 @@
         <v>0</v>
       </c>
       <c r="D1545" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1545" t="b">
         <v>1</v>
@@ -27919,7 +27919,7 @@
         <v>0</v>
       </c>
       <c r="D1546" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1546" t="b">
         <v>1</v>
@@ -27938,7 +27938,7 @@
         <v>0</v>
       </c>
       <c r="D1547" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1547" t="b">
         <v>1</v>
@@ -27957,7 +27957,7 @@
         <v>0</v>
       </c>
       <c r="D1548" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1548" t="b">
         <v>1</v>
@@ -27976,7 +27976,7 @@
         <v>0</v>
       </c>
       <c r="D1549" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1549" t="b">
         <v>1</v>
@@ -27993,7 +27993,7 @@
         <v>0</v>
       </c>
       <c r="D1550" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="E1550" t="b">
         <v>0</v>
@@ -28010,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="D1551" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="E1551" t="b">
         <v>0</v>
@@ -28029,7 +28029,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1552" t="n">
-        <v>-0.2</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1552" t="b">
         <v>1</v>
@@ -28048,7 +28048,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1553" t="n">
-        <v>-0.2</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1553" t="b">
         <v>1</v>
@@ -28163,16 +28163,33 @@
         </is>
       </c>
       <c r="B1560" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="C1560" t="n">
-        <v>-1.428571428571429</v>
+        <v>-2</v>
       </c>
       <c r="D1560" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E1560" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr"/>
+      <c r="C1561" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D1561" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E1561" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -28205,7 +28222,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-04-08 | Publication days: 641</t>
+          <t>Coverage: 2022-01-01 to 2026-04-09 | Publication days: 641</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1561"/>
+  <dimension ref="A1:E1562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28189,6 +28189,23 @@
         <v>-0.6666666666666666</v>
       </c>
       <c r="E1561" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr"/>
+      <c r="C1562" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D1562" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E1562" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28222,7 +28239,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-04-09 | Publication days: 641</t>
+          <t>Coverage: 2022-01-01 to 2026-04-10 | Publication days: 641</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1562"/>
+  <dimension ref="A1:E1563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27138,13 +27138,13 @@
         </is>
       </c>
       <c r="B1503" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1503" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1503" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1503" t="b">
         <v>1</v>
@@ -27160,10 +27160,10 @@
         <v>0</v>
       </c>
       <c r="C1504" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1504" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1504" t="b">
         <v>1</v>
@@ -27179,10 +27179,10 @@
         <v>0</v>
       </c>
       <c r="C1505" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1505" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1505" t="b">
         <v>1</v>
@@ -27198,10 +27198,10 @@
         <v>0</v>
       </c>
       <c r="C1506" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1506" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1506" t="b">
         <v>1</v>
@@ -27215,10 +27215,10 @@
       </c>
       <c r="B1507" t="inlineStr"/>
       <c r="C1507" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1507" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1507" t="b">
         <v>0</v>
@@ -27232,10 +27232,10 @@
       </c>
       <c r="B1508" t="inlineStr"/>
       <c r="C1508" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1508" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1508" t="b">
         <v>0</v>
@@ -27249,10 +27249,10 @@
       </c>
       <c r="B1509" t="inlineStr"/>
       <c r="C1509" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1509" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1509" t="b">
         <v>0</v>
@@ -27271,7 +27271,7 @@
         <v>0</v>
       </c>
       <c r="D1510" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1510" t="b">
         <v>1</v>
@@ -27288,7 +27288,7 @@
         <v>0</v>
       </c>
       <c r="D1511" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1511" t="b">
         <v>0</v>
@@ -27305,7 +27305,7 @@
         <v>0</v>
       </c>
       <c r="D1512" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1512" t="b">
         <v>0</v>
@@ -27324,7 +27324,7 @@
         <v>0</v>
       </c>
       <c r="D1513" t="n">
-        <v>-0.3</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1513" t="b">
         <v>1</v>
@@ -27341,7 +27341,7 @@
         <v>0</v>
       </c>
       <c r="D1514" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1514" t="b">
         <v>0</v>
@@ -27358,7 +27358,7 @@
         <v>0</v>
       </c>
       <c r="D1515" t="n">
-        <v>-0.1</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1515" t="b">
         <v>0</v>
@@ -27377,7 +27377,7 @@
         <v>0</v>
       </c>
       <c r="D1516" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1516" t="b">
         <v>1</v>
@@ -27394,7 +27394,7 @@
         <v>0</v>
       </c>
       <c r="D1517" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1517" t="b">
         <v>0</v>
@@ -27411,7 +27411,7 @@
         <v>0</v>
       </c>
       <c r="D1518" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1518" t="b">
         <v>0</v>
@@ -27428,7 +27428,7 @@
         <v>0</v>
       </c>
       <c r="D1519" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1519" t="b">
         <v>0</v>
@@ -27447,7 +27447,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1520" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1520" t="b">
         <v>1</v>
@@ -27466,7 +27466,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1521" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1521" t="b">
         <v>1</v>
@@ -27479,13 +27479,13 @@
         </is>
       </c>
       <c r="B1522" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C1522" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D1522" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1522" t="b">
         <v>1</v>
@@ -27499,10 +27499,10 @@
       </c>
       <c r="B1523" t="inlineStr"/>
       <c r="C1523" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D1523" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1523" t="b">
         <v>0</v>
@@ -27515,13 +27515,13 @@
         </is>
       </c>
       <c r="B1524" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C1524" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-2</v>
       </c>
       <c r="D1524" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1524" t="b">
         <v>1</v>
@@ -27537,10 +27537,10 @@
         <v>0</v>
       </c>
       <c r="C1525" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-2</v>
       </c>
       <c r="D1525" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1525" t="b">
         <v>1</v>
@@ -27556,10 +27556,10 @@
         <v>0</v>
       </c>
       <c r="C1526" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-2</v>
       </c>
       <c r="D1526" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1526" t="b">
         <v>1</v>
@@ -27575,10 +27575,10 @@
         <v>0</v>
       </c>
       <c r="C1527" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1527" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1527" t="b">
         <v>1</v>
@@ -27592,10 +27592,10 @@
       </c>
       <c r="B1528" t="inlineStr"/>
       <c r="C1528" t="n">
-        <v>0</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1528" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1528" t="b">
         <v>0</v>
@@ -27609,10 +27609,10 @@
       </c>
       <c r="B1529" t="inlineStr"/>
       <c r="C1529" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1529" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1529" t="b">
         <v>0</v>
@@ -27628,10 +27628,10 @@
         <v>0</v>
       </c>
       <c r="C1530" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1530" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1530" t="b">
         <v>1</v>
@@ -27650,7 +27650,7 @@
         <v>0</v>
       </c>
       <c r="D1531" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1531" t="b">
         <v>1</v>
@@ -27667,7 +27667,7 @@
         <v>0</v>
       </c>
       <c r="D1532" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1532" t="b">
         <v>0</v>
@@ -27686,7 +27686,7 @@
         <v>0</v>
       </c>
       <c r="D1533" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1533" t="b">
         <v>1</v>
@@ -27705,7 +27705,7 @@
         <v>0</v>
       </c>
       <c r="D1534" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -27722,7 +27722,7 @@
         <v>0</v>
       </c>
       <c r="D1535" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1535" t="b">
         <v>0</v>
@@ -27739,7 +27739,7 @@
         <v>0</v>
       </c>
       <c r="D1536" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1536" t="b">
         <v>0</v>
@@ -27756,7 +27756,7 @@
         <v>0</v>
       </c>
       <c r="D1537" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1537" t="b">
         <v>0</v>
@@ -27773,7 +27773,7 @@
         <v>0</v>
       </c>
       <c r="D1538" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1538" t="b">
         <v>0</v>
@@ -27792,7 +27792,7 @@
         <v>0</v>
       </c>
       <c r="D1539" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1539" t="b">
         <v>1</v>
@@ -27809,7 +27809,7 @@
         <v>0</v>
       </c>
       <c r="D1540" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1540" t="b">
         <v>0</v>
@@ -27828,7 +27828,7 @@
         <v>0</v>
       </c>
       <c r="D1541" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1541" t="b">
         <v>1</v>
@@ -27845,7 +27845,7 @@
         <v>0</v>
       </c>
       <c r="D1542" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1542" t="b">
         <v>0</v>
@@ -27862,7 +27862,7 @@
         <v>0</v>
       </c>
       <c r="D1543" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1543" t="b">
         <v>0</v>
@@ -27881,7 +27881,7 @@
         <v>0</v>
       </c>
       <c r="D1544" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1544" t="b">
         <v>1</v>
@@ -27900,7 +27900,7 @@
         <v>0</v>
       </c>
       <c r="D1545" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1545" t="b">
         <v>1</v>
@@ -27919,7 +27919,7 @@
         <v>0</v>
       </c>
       <c r="D1546" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1546" t="b">
         <v>1</v>
@@ -27938,7 +27938,7 @@
         <v>0</v>
       </c>
       <c r="D1547" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1547" t="b">
         <v>1</v>
@@ -27957,7 +27957,7 @@
         <v>0</v>
       </c>
       <c r="D1548" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1548" t="b">
         <v>1</v>
@@ -27976,7 +27976,7 @@
         <v>0</v>
       </c>
       <c r="D1549" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1549" t="b">
         <v>1</v>
@@ -27993,7 +27993,7 @@
         <v>0</v>
       </c>
       <c r="D1550" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E1550" t="b">
         <v>0</v>
@@ -28010,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="D1551" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E1551" t="b">
         <v>0</v>
@@ -28029,7 +28029,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1552" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1552" t="b">
         <v>1</v>
@@ -28048,7 +28048,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1553" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1553" t="b">
         <v>1</v>
@@ -28206,6 +28206,23 @@
         <v>-0.7333333333333333</v>
       </c>
       <c r="E1562" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr"/>
+      <c r="C1563" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D1563" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E1563" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28239,7 +28256,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-04-10 | Publication days: 641</t>
+          <t>Coverage: 2022-01-01 to 2026-04-11 | Publication days: 641</t>
         </is>
       </c>
     </row>

--- a/data/BR.xlsx
+++ b/data/BR.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1563"/>
+  <dimension ref="A1:E1564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28223,6 +28223,23 @@
         <v>-0.8</v>
       </c>
       <c r="E1563" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr"/>
+      <c r="C1564" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D1564" t="n">
+        <v>-0.8666666666666667</v>
+      </c>
+      <c r="E1564" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28256,7 +28273,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-01 to 2026-04-11 | Publication days: 641</t>
+          <t>Coverage: 2022-01-01 to 2026-04-12 | Publication days: 641</t>
         </is>
       </c>
     </row>
